--- a/Fase 1 – Análisis del entorno, riesgos y diseño de la solución/Edwin_Gomez/capturas_pruebas_documentos_configuraciones/Matriz Riesgos OWASP 2025 WAF Shield Cloud Edwin Gomez.xlsx
+++ b/Fase 1 – Análisis del entorno, riesgos y diseño de la solución/Edwin_Gomez/capturas_pruebas_documentos_configuraciones/Matriz Riesgos OWASP 2025 WAF Shield Cloud Edwin Gomez.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\analistabi01.iber\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A623A0A8-FA03-4027-AADF-1E7494D7DF78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E88FB8-0D7F-4165-8CB1-E2E5A03E5702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Criterios" sheetId="2" r:id="rId1"/>
@@ -685,6 +685,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -693,15 +702,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1360,16 +1360,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>280147</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>112059</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1583,16 +1583,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="5" t="s">
@@ -1805,104 +1805,104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="30" customHeight="1">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
     </row>
     <row r="2" spans="1:16" ht="23.1" customHeight="1">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="15"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="15"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="18"/>
     </row>
     <row r="3" spans="1:16" ht="23.1" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
-      <c r="P3" s="15"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="18"/>
     </row>
     <row r="4" spans="1:16" ht="23.1" customHeight="1">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="18"/>
     </row>
     <row r="5" spans="1:16" ht="32.1" customHeight="1">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
     </row>
     <row r="7" spans="1:16" ht="42" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -2537,16 +2537,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="14" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
     </row>
     <row r="3" spans="1:8" ht="23.1" customHeight="1">
       <c r="A3" s="10" t="s">
@@ -2567,14 +2567,14 @@
         <v>152</v>
       </c>
       <c r="B4" s="13">
-        <f>COUNTA('Matriz Riesgos OWASP'!A8:A17)</f>
+        <f>COUNTA('Matriz Riesgos OWASP'!$A$8:$A$17)</f>
         <v>10</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>141</v>
       </c>
       <c r="E4" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K8:K17,D4)</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,D4)</f>
         <v>5</v>
       </c>
     </row>
@@ -2583,14 +2583,14 @@
         <v>153</v>
       </c>
       <c r="B5" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K8:K17,"Critico")</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,"Critico")</f>
         <v>5</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>137</v>
       </c>
       <c r="E5" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K9:K18,D5)</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,D5)</f>
         <v>3</v>
       </c>
     </row>
@@ -2599,14 +2599,14 @@
         <v>154</v>
       </c>
       <c r="B6" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K8:K17,"Alto")</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,"Alto")</f>
         <v>3</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>133</v>
       </c>
       <c r="E6" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K10:K19,D6)</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,D6)</f>
         <v>2</v>
       </c>
     </row>
@@ -2615,14 +2615,14 @@
         <v>155</v>
       </c>
       <c r="B7" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K8:K17,"Medio")</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,"Medio")</f>
         <v>2</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>129</v>
       </c>
       <c r="E7" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K11:K20,D7)</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,D7)</f>
         <v>0</v>
       </c>
     </row>
@@ -2631,35 +2631,35 @@
         <v>157</v>
       </c>
       <c r="B8" s="11">
-        <f>COUNTIF('Matriz Riesgos OWASP'!K9:K18,"Bajo")</f>
+        <f>COUNTIF('Matriz Riesgos OWASP'!$K$8:$K$17,"Bajo")</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="19"/>
+      <c r="B10" s="15"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19"/>
+      <c r="A12" s="15"/>
+      <c r="B12" s="15"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
